--- a/project-plan/Sampletasklist.xlsx
+++ b/project-plan/Sampletasklist.xlsx
@@ -2471,7 +2471,7 @@
       <x:c r="I4" s="111"/>
       <x:c r="J4" s="112"/>
       <x:c r="K4" s="70" t="str">
-        <x:v>IDs, owners, evidence fields; request student IDs; retain unconfirmed items as pending</x:v>
+        <x:v>IDs, owners, evidence fields; request student IDs; track open confirmations on Jira</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="51" customFormat="1" ht="64" customHeight="1">
@@ -2552,7 +2552,7 @@
       <x:c r="I7" s="111"/>
       <x:c r="J7" s="112"/>
       <x:c r="K7" s="70" t="str">
-        <x:v>ARC-07; SEC-03/04; no deployment is implied</x:v>
+        <x:v>ARC-07; SEC-03/04; plan only, apply is scheduled in Sprint 2</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="51" customFormat="1" ht="64" customHeight="1">
@@ -2606,7 +2606,7 @@
       <x:c r="I9" s="111"/>
       <x:c r="J9" s="112"/>
       <x:c r="K9" s="70" t="str">
-        <x:v>ARC-04; record actual results rather than assume success</x:v>
+        <x:v>ARC-04; run links and any failed step</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="51" customFormat="1" ht="64" customHeight="1">
@@ -2687,7 +2687,7 @@
       <x:c r="I12" s="114"/>
       <x:c r="J12" s="113"/>
       <x:c r="K12" s="75" t="str">
-        <x:v>Preparation Oct 30; close Nov 1; do not invent review feedback</x:v>
+        <x:v>Preparation Oct 30; close Nov 1; feedback recorded after the review</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="51" customFormat="1" ht="25" customHeight="1">
